--- a/docs/AI智能·学习搭子-V1.0.0/5.运行/用户验证模块测试/测试结果/results_20251013_105650.xlsx
+++ b/docs/AI智能·学习搭子-V1.0.0/5.运行/用户验证模块测试/测试结果/results_20251013_105650.xlsx
@@ -1741,7 +1741,7 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
